--- a/data/trans_camb/IP16B10-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B10-Clase-trans_camb.xlsx
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-80,0; 0,0</t>
+          <t>-76,9; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-41,69; 0,0</t>
+          <t>-40,48; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-74,19; 0,0</t>
+          <t>-65,77; 0,0</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-80,0; 0,0</t>
+          <t>-76,9; 0,0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-41,69; 0,0</t>
+          <t>-40,48; 0,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-74,19; 0,0</t>
+          <t>-65,77; 0,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B10-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B10-Clase-trans_camb.xlsx
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-76,9; 0,0</t>
+          <t>-74,62; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-40,48; 0,0</t>
+          <t>-40,16; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 0,0</t>
+          <t>-65,3; 0,0</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-76,9; 0,0</t>
+          <t>-74,62; 0,0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-40,48; 0,0</t>
+          <t>-40,16; 0,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 0,0</t>
+          <t>-65,3; 0,0</t>
         </is>
       </c>
     </row>
